--- a/SEPTEMBER 2026 - ZONE SALES REPORT.xlsx
+++ b/SEPTEMBER 2026 - ZONE SALES REPORT.xlsx
@@ -20,10 +20,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="[&gt;=10000000]&quot;₹&quot;##\,##\,##\,##0;[&gt;=100000]&quot;₹&quot;##\,##\,##0;&quot;₹&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,70 +32,144 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
+      <color rgb="00C9C9C9"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="20"/>
+      <sz val="10.5"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <i val="1"/>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
+      <color rgb="00141414"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="005A5A5A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00141414"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D02128"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00C4C4C4"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="001A2027"/>
+      <name val="Segoe UI"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="0044515C"/>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="005A5A5A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00141414"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0016537E"/>
+      <color rgb="00D02128"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="005A5A5A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00141414"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="005A5A5A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D02128"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="008A8A8A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00141414"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="001A2027"/>
+      <color rgb="00D02128"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="00C6CDD4"/>
-      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11.5"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000F2D3F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <i val="1"/>
-      <color rgb="008A9BA8"/>
-      <sz val="10"/>
+      <color rgb="008A8A8A"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -104,12 +178,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F2D3F"/>
+        <fgColor rgb="000A0A0A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0016537E"/>
+        <fgColor rgb="00D02128"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A1A1A"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,22 +198,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F7FB"/>
+        <fgColor rgb="00F4F4F4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCEEEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF1F8"/>
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
   </fills>
@@ -148,133 +217,149 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="00E6E6E6"/>
       </left>
       <right style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="00E6E6E6"/>
       </right>
       <top style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="00E6E6E6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="00E6E6E6"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -640,161 +725,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SEPTEMBER 2026  —  ALL-ZONE SALES SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="FFEF4444"/>
+              <sz val="22"/>
+            </rPr>
+            <t>S</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="FFFFFFFF"/>
+              <sz val="22"/>
+            </rPr>
+            <t>EPTEMBER 2026      ALL-ZONE SALES SUMMARY</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Amounts in ₹  •  Totals recomputed from daily brand-wise data</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+          <t>All-Zone Sales Overview   •   Amounts in ₹ (INR)   •   Totals recomputed from daily data</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1"/>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ZONE</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>OPERATING DAYS</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>ACTIVE BRANDS</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>AVG DAILY SALES</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>TOP BRAND</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>ZONE GRAND TOTAL</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>ALPHA 1</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="C5" s="5" t="n">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D6" s="8" t="n">
         <v>15560.89285714286</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>ARROY</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F6" s="10" t="n">
         <v>435705</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>CENTRAL 50</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="C6" s="10" t="n">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>27 days</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D7" s="13" t="n">
         <v>130154.8148148148</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>COFFEE VAULT</t>
         </is>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F7" s="15" t="n">
         <v>3514180</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>BENNETT</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5" t="n">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>27 days</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D8" s="8" t="n">
         <v>136958</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F8" s="10" t="n">
         <v>3697866</v>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>ALL ZONES</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr"/>
-      <c r="C8" s="15" t="inlineStr"/>
-      <c r="D8" s="15" t="inlineStr"/>
-      <c r="E8" s="15" t="inlineStr"/>
-      <c r="F8" s="16" t="n">
+      <c r="B9" s="17" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr"/>
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr"/>
+      <c r="F9" s="18" t="n">
         <v>7647751</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Note: DISTRICT 9 has no September data in the source workbook (only July &amp; August), so it is not included.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -806,927 +919,1089 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ALPHA 1  —  ZONE SALES REPORT</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="FFEF4444"/>
+              <sz val="22"/>
+            </rPr>
+            <t>A</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="FFFFFFFF"/>
+              <sz val="22"/>
+            </rPr>
+            <t>LPHA 1      SEPTEMBER 2026</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>September 2026   •   Day-wise &amp; Brand-wise Sales   •   Amounts in ₹</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+          <t>Day-wise &amp; Brand-wise Sales   •   Amounts in ₹ (INR)   •   Recomputed from daily data</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1"/>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>DAY</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>ARROY</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>TONGUE TWISTER</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>OVENLY GUSTO</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>COFFEE VAULT</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>DAILY TOTAL</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>01 Sep</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C6" s="8" t="n">
         <v>8692</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D6" s="8" t="n">
         <v>2040</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E6" s="8" t="n">
         <v>1878</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F6" s="8" t="n">
         <v>2687</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G6" s="23" t="n">
         <v>15297</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>02 Sep</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C7" s="13" t="n">
         <v>7507</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D7" s="13" t="n">
         <v>2170</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E7" s="13" t="n">
         <v>2935</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F7" s="13" t="n">
         <v>3322</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G7" s="23" t="n">
         <v>15934</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>03 Sep</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C8" s="8" t="n">
         <v>10620</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D8" s="8" t="n">
         <v>1325</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E8" s="8" t="n">
         <v>1274</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F8" s="8" t="n">
         <v>1646</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G8" s="23" t="n">
         <v>14865</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>04 Sep</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C9" s="13" t="n">
         <v>7095</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D9" s="13" t="n">
         <v>1315</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E9" s="13" t="n">
         <v>3432</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F9" s="13" t="n">
         <v>2498</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G9" s="23" t="n">
         <v>14340</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>05 Sep</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C10" s="8" t="n">
         <v>15118</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D10" s="8" t="n">
         <v>3980</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E10" s="8" t="n">
         <v>3601</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F10" s="8" t="n">
         <v>6675</v>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G10" s="23" t="n">
         <v>29374</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>06 Sep</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C11" s="13" t="n">
         <v>14335</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D11" s="13" t="n">
         <v>5560</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E11" s="13" t="n">
         <v>4587</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F11" s="13" t="n">
         <v>2678</v>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G11" s="23" t="n">
         <v>27160</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>07 Sep</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C12" s="8" t="n">
         <v>7970</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D12" s="8" t="n">
         <v>2405</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E12" s="8" t="n">
         <v>3463</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F12" s="8" t="n">
         <v>1856</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G12" s="23" t="n">
         <v>15694</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>08 Sep</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C13" s="13" t="n">
         <v>5874</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D13" s="13" t="n">
         <v>2785</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E13" s="13" t="n">
         <v>2496</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F13" s="13" t="n">
         <v>1115</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G13" s="23" t="n">
         <v>12270</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>09 Sep</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C14" s="8" t="n">
         <v>5950</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D14" s="8" t="n">
         <v>2045</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E14" s="8" t="n">
         <v>2496</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F14" s="8" t="n">
         <v>1241</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G14" s="23" t="n">
         <v>11732</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>10 Sep</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C15" s="13" t="n">
         <v>6951</v>
       </c>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="11" t="n">
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n">
         <v>3073</v>
       </c>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="13" t="n">
+      <c r="F15" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="n">
         <v>10024</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>11 Sep</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C16" s="8" t="n">
         <v>11473</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D16" s="8" t="n">
         <v>1690</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E16" s="8" t="n">
         <v>3281</v>
       </c>
-      <c r="F15" s="26" t="n"/>
-      <c r="G15" s="8" t="n">
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="n">
         <v>16444</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>12 Sep</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C17" s="13" t="n">
         <v>12536</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D17" s="13" t="n">
         <v>3650</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E17" s="13" t="n">
         <v>3580</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F17" s="13" t="n">
         <v>3112</v>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G17" s="23" t="n">
         <v>22878</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>13 Sep</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C18" s="8" t="n">
         <v>16453</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D18" s="8" t="n">
         <v>2770</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E18" s="8" t="n">
         <v>4468</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F18" s="8" t="n">
         <v>6357</v>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="G18" s="23" t="n">
         <v>30048</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>14 Sep</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C19" s="13" t="n">
         <v>10321</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D19" s="13" t="n">
         <v>2215</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E19" s="13" t="n">
         <v>1741</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F19" s="13" t="n">
         <v>814</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="G19" s="23" t="n">
         <v>15091</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>15 Sep</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C20" s="8" t="n">
         <v>7980</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D20" s="8" t="n">
         <v>1900</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E20" s="8" t="n">
         <v>3114</v>
       </c>
-      <c r="F19" s="26" t="n"/>
-      <c r="G19" s="8" t="n">
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="n">
         <v>12994</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>16 Sep</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C21" s="13" t="n">
         <v>5681</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D21" s="13" t="n">
         <v>1680</v>
       </c>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="25" t="n"/>
-      <c r="G20" s="13" t="n">
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="n">
         <v>7361</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>17 Sep</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C22" s="8" t="n">
         <v>5132</v>
       </c>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="6" t="n">
+      <c r="D22" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
         <v>2360</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G22" s="23" t="n">
         <v>7492</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>18 Sep</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C23" s="13" t="n">
         <v>11233</v>
       </c>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="11" t="n">
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
         <v>2728</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G23" s="23" t="n">
         <v>13961</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>19 Sep</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C24" s="8" t="n">
         <v>13390</v>
       </c>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="23" t="n">
+      <c r="D24" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
         <v>4186</v>
       </c>
-      <c r="G23" s="24" t="n">
+      <c r="G24" s="23" t="n">
         <v>17576</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>20 Sep</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C25" s="13" t="n">
         <v>11557</v>
       </c>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="23" t="n">
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
         <v>3622</v>
       </c>
-      <c r="G24" s="24" t="n">
+      <c r="G25" s="23" t="n">
         <v>15179</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>21 Sep</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C26" s="8" t="n">
         <v>8940</v>
       </c>
-      <c r="D25" s="26" t="n"/>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="6" t="n">
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
         <v>2231</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G26" s="23" t="n">
         <v>11171</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>22 Sep</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C27" s="13" t="n">
         <v>9760</v>
       </c>
-      <c r="D26" s="25" t="n"/>
-      <c r="E26" s="25" t="n"/>
-      <c r="F26" s="11" t="n">
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
         <v>2616</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="G27" s="23" t="n">
         <v>12376</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>23 Sep</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C28" s="8" t="n">
         <v>8319</v>
       </c>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="6" t="n">
+      <c r="D28" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n">
         <v>3897</v>
       </c>
-      <c r="G27" s="8" t="n">
+      <c r="G28" s="23" t="n">
         <v>12216</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>24 Sep</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C29" s="13" t="n">
         <v>8630</v>
       </c>
-      <c r="D28" s="25" t="n"/>
-      <c r="E28" s="25" t="n"/>
-      <c r="F28" s="11" t="n">
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
         <v>3550</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="G29" s="23" t="n">
         <v>12180</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>25 Sep</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C30" s="8" t="n">
         <v>9553</v>
       </c>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="26" t="n"/>
-      <c r="G29" s="8" t="n">
+      <c r="D30" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F30" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="n">
         <v>9553</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>26 Sep</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C31" s="13" t="n">
         <v>15934</v>
       </c>
-      <c r="D30" s="27" t="n"/>
-      <c r="E30" s="27" t="n"/>
-      <c r="F30" s="23" t="n">
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="n">
         <v>4133</v>
       </c>
-      <c r="G30" s="24" t="n">
+      <c r="G31" s="23" t="n">
         <v>20067</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>27 Sep</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C32" s="8" t="n">
         <v>17719</v>
       </c>
-      <c r="D31" s="27" t="n"/>
-      <c r="E31" s="27" t="n"/>
-      <c r="F31" s="23" t="n">
+      <c r="D32" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
         <v>6254</v>
       </c>
-      <c r="G31" s="24" t="n">
+      <c r="G32" s="23" t="n">
         <v>23973</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>28 Sep</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C33" s="13" t="n">
         <v>8455</v>
       </c>
-      <c r="D32" s="25" t="n"/>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="25" t="n"/>
-      <c r="G32" s="13" t="n">
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="n">
         <v>8455</v>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B33" s="28" t="inlineStr"/>
-      <c r="C33" s="29" t="n">
+      <c r="B34" s="30" t="inlineStr"/>
+      <c r="C34" s="31" t="n">
         <v>283178</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D34" s="31" t="n">
         <v>37530</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E34" s="31" t="n">
         <v>45419</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F34" s="31" t="n">
         <v>69578</v>
       </c>
-      <c r="G33" s="30" t="n">
+      <c r="G34" s="32" t="n">
         <v>435705</v>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="31" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>SHARE %</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr"/>
-      <c r="C34" s="32" t="n">
+      <c r="B35" s="34" t="inlineStr"/>
+      <c r="C35" s="35" t="n">
         <v>0.6499305722908849</v>
       </c>
-      <c r="D34" s="32" t="n">
+      <c r="D35" s="36" t="n">
         <v>0.08613626192033601</v>
       </c>
-      <c r="E34" s="32" t="n">
+      <c r="E35" s="36" t="n">
         <v>0.1042425494313813</v>
       </c>
-      <c r="F34" s="32" t="n">
+      <c r="F35" s="36" t="n">
         <v>0.1596906163573978</v>
       </c>
-      <c r="G34" s="33" t="n">
+      <c r="G35" s="37" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="34" t="inlineStr">
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="38" t="inlineStr">
         <is>
           <t>ZONE SUMMARY  —  September 2026</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="35" t="inlineStr">
+    <row r="38" ht="3" customHeight="1">
+      <c r="A38" s="3" t="n"/>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="A39" s="39" t="inlineStr">
         <is>
           <t>Zone Grand Total</t>
         </is>
       </c>
-      <c r="B37" s="36" t="inlineStr">
-        <is>
-          <t>₹435,705</t>
-        </is>
-      </c>
-      <c r="C37" s="37" t="n"/>
-      <c r="D37" s="37" t="n"/>
-      <c r="E37" s="37" t="n"/>
-      <c r="F37" s="37" t="n"/>
-      <c r="G37" s="37" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="B39" s="40" t="inlineStr">
+        <is>
+          <t>₹4,35,705</t>
+        </is>
+      </c>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="41" t="n"/>
+      <c r="E39" s="41" t="n"/>
+      <c r="F39" s="41" t="n"/>
+      <c r="G39" s="41" t="n"/>
+    </row>
+    <row r="40" ht="21" customHeight="1">
+      <c r="A40" s="39" t="inlineStr">
         <is>
           <t>Operating Days</t>
         </is>
       </c>
-      <c r="B38" s="36" t="inlineStr">
+      <c r="B40" s="42" t="inlineStr">
         <is>
           <t>28 days</t>
         </is>
       </c>
-      <c r="C38" s="37" t="n"/>
-      <c r="D38" s="37" t="n"/>
-      <c r="E38" s="37" t="n"/>
-      <c r="F38" s="37" t="n"/>
-      <c r="G38" s="37" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="C40" s="41" t="n"/>
+      <c r="D40" s="41" t="n"/>
+      <c r="E40" s="41" t="n"/>
+      <c r="F40" s="41" t="n"/>
+      <c r="G40" s="41" t="n"/>
+    </row>
+    <row r="41" ht="21" customHeight="1">
+      <c r="A41" s="39" t="inlineStr">
         <is>
           <t>Average Daily Sales</t>
         </is>
       </c>
-      <c r="B39" s="36" t="inlineStr">
+      <c r="B41" s="42" t="inlineStr">
         <is>
           <t>₹15,561</t>
         </is>
       </c>
-      <c r="C39" s="37" t="n"/>
-      <c r="D39" s="37" t="n"/>
-      <c r="E39" s="37" t="n"/>
-      <c r="F39" s="37" t="n"/>
-      <c r="G39" s="37" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="C41" s="41" t="n"/>
+      <c r="D41" s="41" t="n"/>
+      <c r="E41" s="41" t="n"/>
+      <c r="F41" s="41" t="n"/>
+      <c r="G41" s="41" t="n"/>
+    </row>
+    <row r="42" ht="21" customHeight="1">
+      <c r="A42" s="39" t="inlineStr">
         <is>
           <t>Best Sales Day</t>
         </is>
       </c>
-      <c r="B40" s="36" t="inlineStr">
-        <is>
-          <t>13 Sep (Sunday) — ₹30,048</t>
-        </is>
-      </c>
-      <c r="C40" s="37" t="n"/>
-      <c r="D40" s="37" t="n"/>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="37" t="n"/>
-      <c r="G40" s="37" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="35" t="inlineStr">
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>13 Sep (Sunday)  •  ₹30,048</t>
+        </is>
+      </c>
+      <c r="C42" s="41" t="n"/>
+      <c r="D42" s="41" t="n"/>
+      <c r="E42" s="41" t="n"/>
+      <c r="F42" s="41" t="n"/>
+      <c r="G42" s="41" t="n"/>
+    </row>
+    <row r="43" ht="21" customHeight="1">
+      <c r="A43" s="39" t="inlineStr">
         <is>
           <t>Top Brand</t>
         </is>
       </c>
-      <c r="B41" s="36" t="inlineStr">
-        <is>
-          <t>ARROY — ₹283,178 (65.0%)</t>
-        </is>
-      </c>
-      <c r="C41" s="37" t="n"/>
-      <c r="D41" s="37" t="n"/>
-      <c r="E41" s="37" t="n"/>
-      <c r="F41" s="37" t="n"/>
-      <c r="G41" s="37" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="35" t="inlineStr">
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>ARROY  •  ₹2,83,178  (65.0%)</t>
+        </is>
+      </c>
+      <c r="C43" s="41" t="n"/>
+      <c r="D43" s="41" t="n"/>
+      <c r="E43" s="41" t="n"/>
+      <c r="F43" s="41" t="n"/>
+      <c r="G43" s="41" t="n"/>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="39" t="inlineStr">
         <is>
           <t>Active Brands</t>
         </is>
       </c>
-      <c r="B42" s="36" t="inlineStr">
+      <c r="B44" s="42" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C42" s="37" t="n"/>
-      <c r="D42" s="37" t="n"/>
-      <c r="E42" s="37" t="n"/>
-      <c r="F42" s="37" t="n"/>
-      <c r="G42" s="37" t="n"/>
+      <c r="C44" s="41" t="n"/>
+      <c r="D44" s="41" t="n"/>
+      <c r="E44" s="41" t="n"/>
+      <c r="F44" s="41" t="n"/>
+      <c r="G44" s="41" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>Weekends shown in red • – denotes no recorded sale • all totals recomputed from daily brand-wise figures</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="A36:G36"/>
+  <mergeCells count="12">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B42:G42"/>
-    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A3:G3"/>
     <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
     <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1738,1051 +2013,1109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CENTRAL 50  —  ZONE SALES REPORT</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="FFEF4444"/>
+              <sz val="22"/>
+            </rPr>
+            <t>C</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="FFFFFFFF"/>
+              <sz val="22"/>
+            </rPr>
+            <t>ENTRAL 50      SEPTEMBER 2026</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>September 2026   •   Day-wise &amp; Brand-wise Sales   •   Amounts in ₹</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+          <t>Day-wise &amp; Brand-wise Sales   •   Amounts in ₹ (INR)   •   Recomputed from daily data</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1"/>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>DAY</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>COFFEE VAULT</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>CHATPATA AFFAIR</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>MOMO BOX</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>UMAMI-D-KITCHEN</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>SAUSAGE SALON</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>DAILY TOTAL</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>01 Sep</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C6" s="8" t="n">
         <v>17549</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D6" s="8" t="n">
         <v>9232</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E6" s="8" t="n">
         <v>20718</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F6" s="8" t="n">
         <v>7287</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G6" s="8" t="n">
         <v>8898</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H6" s="23" t="n">
         <v>63684</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>02 Sep</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C7" s="13" t="n">
         <v>29793</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D7" s="13" t="n">
         <v>18699</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E7" s="13" t="n">
         <v>24881</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F7" s="13" t="n">
         <v>8232</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G7" s="13" t="n">
         <v>12509</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H7" s="23" t="n">
         <v>94114</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>03 Sep</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C8" s="8" t="n">
         <v>20814</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D8" s="8" t="n">
         <v>20072</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E8" s="8" t="n">
         <v>23674</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F8" s="8" t="n">
         <v>18225</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G8" s="8" t="n">
         <v>15119</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H8" s="23" t="n">
         <v>97904</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>04 Sep</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C9" s="13" t="n">
         <v>23498</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D9" s="13" t="n">
         <v>14672</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E9" s="13" t="n">
         <v>23200</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F9" s="13" t="n">
         <v>10817</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G9" s="13" t="n">
         <v>14340</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H9" s="23" t="n">
         <v>86527</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>05 Sep</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C10" s="8" t="n">
         <v>60927</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D10" s="8" t="n">
         <v>33009</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E10" s="8" t="n">
         <v>70615</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F10" s="8" t="n">
         <v>34184</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G10" s="8" t="n">
         <v>34250</v>
       </c>
-      <c r="H9" s="24" t="n">
+      <c r="H10" s="23" t="n">
         <v>232985</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>06 Sep</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C11" s="13" t="n">
         <v>74767</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D11" s="13" t="n">
         <v>41148</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E11" s="13" t="n">
         <v>60464</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F11" s="13" t="n">
         <v>32988</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G11" s="13" t="n">
         <v>43877</v>
       </c>
-      <c r="H10" s="24" t="n">
+      <c r="H11" s="23" t="n">
         <v>253244</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>07 Sep</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C12" s="8" t="n">
         <v>30850</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D12" s="8" t="n">
         <v>10691</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E12" s="8" t="n">
         <v>26623</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F12" s="8" t="n">
         <v>10929</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G12" s="8" t="n">
         <v>17098</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H12" s="23" t="n">
         <v>96191</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>08 Sep</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C13" s="13" t="n">
         <v>27872</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D13" s="13" t="n">
         <v>10921</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E13" s="13" t="n">
         <v>22882</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F13" s="13" t="n">
         <v>10178</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G13" s="13" t="n">
         <v>15046</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H13" s="23" t="n">
         <v>86899</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>09 Sep</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C14" s="8" t="n">
         <v>28175</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D14" s="8" t="n">
         <v>14003</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E14" s="8" t="n">
         <v>23179</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F14" s="8" t="n">
         <v>12464</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G14" s="8" t="n">
         <v>11216</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H14" s="23" t="n">
         <v>89037</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>10 Sep</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C15" s="13" t="n">
         <v>26677</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D15" s="13" t="n">
         <v>17230</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E15" s="13" t="n">
         <v>25496</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F15" s="13" t="n">
         <v>9989</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G15" s="13" t="n">
         <v>11639</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H15" s="23" t="n">
         <v>91031</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>11 Sep</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C16" s="8" t="n">
         <v>35131</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D16" s="8" t="n">
         <v>22769</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E16" s="8" t="n">
         <v>36613</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F16" s="8" t="n">
         <v>18637</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G16" s="8" t="n">
         <v>22327</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H16" s="23" t="n">
         <v>135477</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>12 Sep</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C17" s="13" t="n">
         <v>74337</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D17" s="13" t="n">
         <v>41066</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E17" s="13" t="n">
         <v>71907</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F17" s="13" t="n">
         <v>24739</v>
       </c>
-      <c r="G16" s="23" t="n">
+      <c r="G17" s="13" t="n">
         <v>36125</v>
       </c>
-      <c r="H16" s="24" t="n">
+      <c r="H17" s="23" t="n">
         <v>248174</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>13 Sep</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C18" s="8" t="n">
         <v>66843</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D18" s="8" t="n">
         <v>42637</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E18" s="8" t="n">
         <v>58970</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F18" s="8" t="n">
         <v>28271</v>
       </c>
-      <c r="G17" s="23" t="n">
+      <c r="G18" s="8" t="n">
         <v>47519</v>
       </c>
-      <c r="H17" s="24" t="n">
+      <c r="H18" s="23" t="n">
         <v>244240</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>14 Sep</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C19" s="13" t="n">
         <v>26863</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D19" s="13" t="n">
         <v>15761</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E19" s="13" t="n">
         <v>19474</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F19" s="13" t="n">
         <v>10358</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G19" s="13" t="n">
         <v>16891</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H19" s="23" t="n">
         <v>89347</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>15 Sep</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C20" s="8" t="n">
         <v>26429</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D20" s="8" t="n">
         <v>13098</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E20" s="8" t="n">
         <v>19607</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F20" s="8" t="n">
         <v>9022</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G20" s="8" t="n">
         <v>15609</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H20" s="23" t="n">
         <v>83765</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>16 Sep</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C21" s="13" t="n">
         <v>15839</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D21" s="13" t="n">
         <v>16419</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E21" s="13" t="n">
         <v>26386</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F21" s="13" t="n">
         <v>7401</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G21" s="13" t="n">
         <v>13813</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="H21" s="23" t="n">
         <v>79858</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>17 Sep</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C22" s="8" t="n">
         <v>31967</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D22" s="8" t="n">
         <v>18297</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E22" s="8" t="n">
         <v>29457</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F22" s="8" t="n">
         <v>9847</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G22" s="8" t="n">
         <v>19442</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H22" s="23" t="n">
         <v>109010</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>18 Sep</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C23" s="13" t="n">
         <v>33719</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D23" s="13" t="n">
         <v>21398</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E23" s="13" t="n">
         <v>27581</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F23" s="13" t="n">
         <v>21331</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G23" s="13" t="n">
         <v>19409</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="H23" s="23" t="n">
         <v>123438</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>19 Sep</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C24" s="8" t="n">
         <v>59554</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D24" s="8" t="n">
         <v>40918</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E24" s="8" t="n">
         <v>60816</v>
       </c>
-      <c r="F23" s="23" t="n">
+      <c r="F24" s="8" t="n">
         <v>30348</v>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="G24" s="8" t="n">
         <v>37412</v>
       </c>
-      <c r="H23" s="24" t="n">
+      <c r="H24" s="23" t="n">
         <v>229048</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>20 Sep</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C25" s="13" t="n">
         <v>54917</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D25" s="13" t="n">
         <v>47545</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E25" s="13" t="n">
         <v>61324</v>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F25" s="13" t="n">
         <v>27138</v>
       </c>
-      <c r="G24" s="23" t="n">
+      <c r="G25" s="13" t="n">
         <v>38553</v>
       </c>
-      <c r="H24" s="24" t="n">
+      <c r="H25" s="23" t="n">
         <v>229477</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>21 Sep</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C26" s="8" t="n">
         <v>19354</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D26" s="8" t="n">
         <v>15579</v>
       </c>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="6" t="n">
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
         <v>9861</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G26" s="8" t="n">
         <v>13754</v>
       </c>
-      <c r="H25" s="8" t="n">
+      <c r="H26" s="23" t="n">
         <v>58548</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>22 Sep</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C27" s="13" t="n">
         <v>16269</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D27" s="13" t="n">
         <v>13343</v>
       </c>
-      <c r="E26" s="25" t="n"/>
-      <c r="F26" s="11" t="n">
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
         <v>11271</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G27" s="13" t="n">
         <v>14160</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="H27" s="23" t="n">
         <v>55043</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>23 Sep</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C28" s="8" t="n">
         <v>24649</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D28" s="8" t="n">
         <v>14269</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E28" s="8" t="n">
         <v>22359</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F28" s="8" t="n">
         <v>11312</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G28" s="8" t="n">
         <v>13856</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H28" s="23" t="n">
         <v>86445</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>24 Sep</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C29" s="13" t="n">
         <v>28689</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D29" s="13" t="n">
         <v>14520</v>
       </c>
-      <c r="E28" s="25" t="n"/>
-      <c r="F28" s="11" t="n">
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
         <v>14560</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G29" s="13" t="n">
         <v>23531</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="H29" s="23" t="n">
         <v>81300</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>25 Sep</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C30" s="8" t="n">
         <v>37148</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D30" s="8" t="n">
         <v>25116</v>
       </c>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="6" t="n">
+      <c r="E30" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
         <v>19756</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G30" s="8" t="n">
         <v>26399</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H30" s="23" t="n">
         <v>108419</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>26 Sep</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C31" s="13" t="n">
         <v>50635</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D31" s="13" t="n">
         <v>24420</v>
       </c>
-      <c r="E30" s="27" t="n"/>
-      <c r="F30" s="23" t="n">
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="n">
         <v>21682</v>
       </c>
-      <c r="G30" s="23" t="n">
+      <c r="G31" s="13" t="n">
         <v>30988</v>
       </c>
-      <c r="H30" s="24" t="n">
+      <c r="H31" s="23" t="n">
         <v>127725</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>27 Sep</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C32" s="8" t="n">
         <v>78248</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D32" s="8" t="n">
         <v>40661</v>
       </c>
-      <c r="E31" s="27" t="n"/>
-      <c r="F31" s="23" t="n">
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
         <v>53655</v>
       </c>
-      <c r="G31" s="23" t="n">
+      <c r="G32" s="8" t="n">
         <v>60686</v>
       </c>
-      <c r="H31" s="24" t="n">
+      <c r="H32" s="23" t="n">
         <v>233250</v>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B32" s="28" t="inlineStr"/>
-      <c r="C32" s="29" t="n">
+      <c r="B33" s="30" t="inlineStr"/>
+      <c r="C33" s="31" t="n">
         <v>1021513</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D33" s="31" t="n">
         <v>617493</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E33" s="31" t="n">
         <v>756226</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F33" s="31" t="n">
         <v>484482</v>
       </c>
-      <c r="G32" s="29" t="n">
+      <c r="G33" s="31" t="n">
         <v>634466</v>
       </c>
-      <c r="H32" s="30" t="n">
+      <c r="H33" s="32" t="n">
         <v>3514180</v>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="31" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t>SHARE %</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="32" t="n">
+      <c r="B34" s="34" t="inlineStr"/>
+      <c r="C34" s="35" t="n">
         <v>0.2906831750223381</v>
       </c>
-      <c r="D33" s="32" t="n">
+      <c r="D34" s="36" t="n">
         <v>0.1757146759699275</v>
       </c>
-      <c r="E33" s="32" t="n">
+      <c r="E34" s="36" t="n">
         <v>0.215192733439949</v>
       </c>
-      <c r="F33" s="32" t="n">
+      <c r="F34" s="36" t="n">
         <v>0.1378648788622097</v>
       </c>
-      <c r="G33" s="32" t="n">
+      <c r="G34" s="36" t="n">
         <v>0.1805445367055757</v>
       </c>
-      <c r="H33" s="33" t="n">
+      <c r="H34" s="37" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="34" t="inlineStr">
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="38" t="inlineStr">
         <is>
           <t>ZONE SUMMARY  —  September 2026</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+    <row r="37" ht="3" customHeight="1">
+      <c r="A37" s="3" t="n"/>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="39" t="inlineStr">
         <is>
           <t>Zone Grand Total</t>
         </is>
       </c>
-      <c r="B36" s="36" t="inlineStr">
-        <is>
-          <t>₹3,514,180</t>
-        </is>
-      </c>
-      <c r="C36" s="37" t="n"/>
-      <c r="D36" s="37" t="n"/>
-      <c r="E36" s="37" t="n"/>
-      <c r="F36" s="37" t="n"/>
-      <c r="G36" s="37" t="n"/>
-      <c r="H36" s="37" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
+        <is>
+          <t>₹35,14,180</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="n"/>
+      <c r="D38" s="41" t="n"/>
+      <c r="E38" s="41" t="n"/>
+      <c r="F38" s="41" t="n"/>
+      <c r="G38" s="41" t="n"/>
+      <c r="H38" s="41" t="n"/>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="A39" s="39" t="inlineStr">
         <is>
           <t>Operating Days</t>
         </is>
       </c>
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B39" s="42" t="inlineStr">
         <is>
           <t>27 days</t>
         </is>
       </c>
-      <c r="C37" s="37" t="n"/>
-      <c r="D37" s="37" t="n"/>
-      <c r="E37" s="37" t="n"/>
-      <c r="F37" s="37" t="n"/>
-      <c r="G37" s="37" t="n"/>
-      <c r="H37" s="37" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="41" t="n"/>
+      <c r="E39" s="41" t="n"/>
+      <c r="F39" s="41" t="n"/>
+      <c r="G39" s="41" t="n"/>
+      <c r="H39" s="41" t="n"/>
+    </row>
+    <row r="40" ht="21" customHeight="1">
+      <c r="A40" s="39" t="inlineStr">
         <is>
           <t>Average Daily Sales</t>
         </is>
       </c>
-      <c r="B38" s="36" t="inlineStr">
-        <is>
-          <t>₹130,155</t>
-        </is>
-      </c>
-      <c r="C38" s="37" t="n"/>
-      <c r="D38" s="37" t="n"/>
-      <c r="E38" s="37" t="n"/>
-      <c r="F38" s="37" t="n"/>
-      <c r="G38" s="37" t="n"/>
-      <c r="H38" s="37" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="B40" s="42" t="inlineStr">
+        <is>
+          <t>₹1,30,155</t>
+        </is>
+      </c>
+      <c r="C40" s="41" t="n"/>
+      <c r="D40" s="41" t="n"/>
+      <c r="E40" s="41" t="n"/>
+      <c r="F40" s="41" t="n"/>
+      <c r="G40" s="41" t="n"/>
+      <c r="H40" s="41" t="n"/>
+    </row>
+    <row r="41" ht="21" customHeight="1">
+      <c r="A41" s="39" t="inlineStr">
         <is>
           <t>Best Sales Day</t>
         </is>
       </c>
-      <c r="B39" s="36" t="inlineStr">
-        <is>
-          <t>06 Sep (Sunday) — ₹253,244</t>
-        </is>
-      </c>
-      <c r="C39" s="37" t="n"/>
-      <c r="D39" s="37" t="n"/>
-      <c r="E39" s="37" t="n"/>
-      <c r="F39" s="37" t="n"/>
-      <c r="G39" s="37" t="n"/>
-      <c r="H39" s="37" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="B41" s="42" t="inlineStr">
+        <is>
+          <t>06 Sep (Sunday)  •  ₹2,53,244</t>
+        </is>
+      </c>
+      <c r="C41" s="41" t="n"/>
+      <c r="D41" s="41" t="n"/>
+      <c r="E41" s="41" t="n"/>
+      <c r="F41" s="41" t="n"/>
+      <c r="G41" s="41" t="n"/>
+      <c r="H41" s="41" t="n"/>
+    </row>
+    <row r="42" ht="21" customHeight="1">
+      <c r="A42" s="39" t="inlineStr">
         <is>
           <t>Top Brand</t>
         </is>
       </c>
-      <c r="B40" s="36" t="inlineStr">
-        <is>
-          <t>COFFEE VAULT — ₹1,021,513 (29.1%)</t>
-        </is>
-      </c>
-      <c r="C40" s="37" t="n"/>
-      <c r="D40" s="37" t="n"/>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="37" t="n"/>
-      <c r="G40" s="37" t="n"/>
-      <c r="H40" s="37" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="35" t="inlineStr">
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>COFFEE VAULT  •  ₹10,21,513  (29.1%)</t>
+        </is>
+      </c>
+      <c r="C42" s="41" t="n"/>
+      <c r="D42" s="41" t="n"/>
+      <c r="E42" s="41" t="n"/>
+      <c r="F42" s="41" t="n"/>
+      <c r="G42" s="41" t="n"/>
+      <c r="H42" s="41" t="n"/>
+    </row>
+    <row r="43" ht="21" customHeight="1">
+      <c r="A43" s="39" t="inlineStr">
         <is>
           <t>Active Brands</t>
         </is>
       </c>
-      <c r="B41" s="36" t="inlineStr">
+      <c r="B43" s="42" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C41" s="37" t="n"/>
-      <c r="D41" s="37" t="n"/>
-      <c r="E41" s="37" t="n"/>
-      <c r="F41" s="37" t="n"/>
-      <c r="G41" s="37" t="n"/>
-      <c r="H41" s="37" t="n"/>
+      <c r="C43" s="41" t="n"/>
+      <c r="D43" s="41" t="n"/>
+      <c r="E43" s="41" t="n"/>
+      <c r="F43" s="41" t="n"/>
+      <c r="G43" s="41" t="n"/>
+      <c r="H43" s="41" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>Weekends shown in red • – denotes no recorded sale • all totals recomputed from daily brand-wise figures</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B36:H36"/>
+  <mergeCells count="12">
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="B40:H40"/>
-    <mergeCell ref="A35:H35"/>
     <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B38:H38"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2794,1417 +3127,1535 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BENNETT  —  ZONE SALES REPORT</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="FFEF4444"/>
+              <sz val="22"/>
+            </rPr>
+            <t>B</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="FFFFFFFF"/>
+              <sz val="22"/>
+            </rPr>
+            <t>ENNETT      SEPTEMBER 2026</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>September 2026   •   Day-wise &amp; Brand-wise Sales   •   Amounts in ₹</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+          <t>Day-wise &amp; Brand-wise Sales   •   Amounts in ₹ (INR)   •   Recomputed from daily data</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1"/>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>DAY</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>ZORKO</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>OG PIZZA</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>MOMO BOX</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>THE COFFEE VAULT</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>EGGSPERT</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>KOBYS</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>BBF</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>THE CHATPATA AFFAIR</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t>DAILY TOTAL</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>01 Sep</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n"/>
-      <c r="D5" s="6" t="n">
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>12215</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E6" s="8" t="n">
         <v>13248</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F6" s="8" t="n">
         <v>16202</v>
       </c>
-      <c r="G5" s="26" t="n"/>
-      <c r="H5" s="6" t="n">
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
         <v>7911</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I6" s="8" t="n">
         <v>8481</v>
       </c>
-      <c r="J5" s="26" t="n"/>
-      <c r="K5" s="6" t="n">
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="n">
         <v>7498</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L6" s="23" t="n">
         <v>65555</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>02 Sep</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n"/>
-      <c r="D6" s="11" t="n">
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
         <v>25793</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E7" s="13" t="n">
         <v>19941</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F7" s="13" t="n">
         <v>18658</v>
       </c>
-      <c r="G6" s="25" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="n">
         <v>14570</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I7" s="13" t="n">
         <v>12876</v>
       </c>
-      <c r="J6" s="25" t="n"/>
-      <c r="K6" s="11" t="n">
+      <c r="J7" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
         <v>10412</v>
       </c>
-      <c r="L6" s="13" t="n">
+      <c r="L7" s="23" t="n">
         <v>102250</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>03 Sep</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C8" s="8" t="n">
         <v>11047</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D8" s="8" t="n">
         <v>18126</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E8" s="8" t="n">
         <v>11117</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F8" s="8" t="n">
         <v>13463</v>
       </c>
-      <c r="G7" s="26" t="n"/>
-      <c r="H7" s="6" t="n">
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>12732</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I8" s="8" t="n">
         <v>10857</v>
       </c>
-      <c r="J7" s="26" t="n"/>
-      <c r="K7" s="6" t="n">
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="n">
         <v>6703</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L8" s="23" t="n">
         <v>84045</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>04 Sep</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C9" s="13" t="n">
         <v>18712</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D9" s="13" t="n">
         <v>10216</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E9" s="13" t="n">
         <v>6594</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F9" s="13" t="n">
         <v>9226</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G9" s="13" t="n">
         <v>12684</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H9" s="13" t="n">
         <v>1467</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I9" s="13" t="n">
         <v>5194</v>
       </c>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="11" t="n">
+      <c r="J9" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
         <v>4782</v>
       </c>
-      <c r="L8" s="13" t="n">
+      <c r="L9" s="23" t="n">
         <v>68875</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>05 Sep</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C10" s="8" t="n">
         <v>19172</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D10" s="8" t="n">
         <v>7708</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E10" s="8" t="n">
         <v>6363</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F10" s="8" t="n">
         <v>10538</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G10" s="8" t="n">
         <v>40504</v>
       </c>
-      <c r="H9" s="23" t="n">
+      <c r="H10" s="8" t="n">
         <v>5032</v>
       </c>
-      <c r="I9" s="23" t="n">
+      <c r="I10" s="8" t="n">
         <v>6014</v>
       </c>
-      <c r="J9" s="27" t="n"/>
-      <c r="K9" s="23" t="n">
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="n">
         <v>5929</v>
       </c>
-      <c r="L9" s="24" t="n">
+      <c r="L10" s="23" t="n">
         <v>101260</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>06 Sep</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C11" s="13" t="n">
         <v>24458</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D11" s="13" t="n">
         <v>14219</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E11" s="13" t="n">
         <v>10851</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F11" s="13" t="n">
         <v>15529</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G11" s="13" t="n">
         <v>58521</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H11" s="13" t="n">
         <v>8970</v>
       </c>
-      <c r="I10" s="23" t="n">
+      <c r="I11" s="13" t="n">
         <v>6604</v>
       </c>
-      <c r="J10" s="27" t="n"/>
-      <c r="K10" s="23" t="n">
+      <c r="J11" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
         <v>4334</v>
       </c>
-      <c r="L10" s="24" t="n">
+      <c r="L11" s="23" t="n">
         <v>143486</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>07 Sep</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C12" s="8" t="n">
         <v>26275</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D12" s="8" t="n">
         <v>16920</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E12" s="8" t="n">
         <v>11816</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F12" s="8" t="n">
         <v>16638</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G12" s="8" t="n">
         <v>52699</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H12" s="8" t="n">
         <v>4987</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I12" s="8" t="n">
         <v>12066</v>
       </c>
-      <c r="J11" s="26" t="n"/>
-      <c r="K11" s="6" t="n">
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="n">
         <v>5929</v>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="L12" s="23" t="n">
         <v>147330</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>08 Sep</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C13" s="13" t="n">
         <v>30779</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D13" s="13" t="n">
         <v>11779</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E13" s="13" t="n">
         <v>10444</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F13" s="13" t="n">
         <v>17610</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G13" s="13" t="n">
         <v>67188</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H13" s="13" t="n">
         <v>8437</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I13" s="13" t="n">
         <v>13937</v>
       </c>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="11" t="n">
+      <c r="J13" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
         <v>7648</v>
       </c>
-      <c r="L12" s="13" t="n">
+      <c r="L13" s="23" t="n">
         <v>167822</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>09 Sep</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C14" s="8" t="n">
         <v>24580</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D14" s="8" t="n">
         <v>13760</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E14" s="8" t="n">
         <v>11487</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F14" s="8" t="n">
         <v>15170</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G14" s="8" t="n">
         <v>57129</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H14" s="8" t="n">
         <v>9468</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I14" s="8" t="n">
         <v>11864</v>
       </c>
-      <c r="J13" s="26" t="n"/>
-      <c r="K13" s="6" t="n">
+      <c r="J14" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="n">
         <v>6185</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L14" s="23" t="n">
         <v>149643</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>10 Sep</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C15" s="13" t="n">
         <v>24510</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D15" s="13" t="n">
         <v>15090</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E15" s="13" t="n">
         <v>11483</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F15" s="13" t="n">
         <v>19422</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G15" s="13" t="n">
         <v>70572</v>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H15" s="13" t="n">
         <v>7999</v>
       </c>
-      <c r="I14" s="11" t="n">
+      <c r="I15" s="13" t="n">
         <v>9795</v>
       </c>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="11" t="n">
+      <c r="J15" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
         <v>5464</v>
       </c>
-      <c r="L14" s="13" t="n">
+      <c r="L15" s="23" t="n">
         <v>164335</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>11 Sep</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C16" s="8" t="n">
         <v>33564</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D16" s="8" t="n">
         <v>14483</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E16" s="8" t="n">
         <v>7936</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F16" s="8" t="n">
         <v>14448</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G16" s="8" t="n">
         <v>72821</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H16" s="8" t="n">
         <v>6611</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I16" s="8" t="n">
         <v>10433</v>
       </c>
-      <c r="J15" s="26" t="n"/>
-      <c r="K15" s="6" t="n">
+      <c r="J16" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="n">
         <v>7310</v>
       </c>
-      <c r="L15" s="8" t="n">
+      <c r="L16" s="23" t="n">
         <v>167606</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>12 Sep</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C17" s="13" t="n">
         <v>25902</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D17" s="13" t="n">
         <v>14391</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E17" s="13" t="n">
         <v>5909</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F17" s="13" t="n">
         <v>13580</v>
       </c>
-      <c r="G16" s="23" t="n">
+      <c r="G17" s="13" t="n">
         <v>68502</v>
       </c>
-      <c r="H16" s="23" t="n">
+      <c r="H17" s="13" t="n">
         <v>4173</v>
       </c>
-      <c r="I16" s="23" t="n">
+      <c r="I17" s="13" t="n">
         <v>9278</v>
       </c>
-      <c r="J16" s="27" t="n"/>
-      <c r="K16" s="23" t="n">
+      <c r="J17" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
         <v>4368</v>
       </c>
-      <c r="L16" s="24" t="n">
+      <c r="L17" s="23" t="n">
         <v>146103</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>13 Sep</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C18" s="8" t="n">
         <v>23496</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D18" s="8" t="n">
         <v>13083</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E18" s="8" t="n">
         <v>4038</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F18" s="8" t="n">
         <v>9366</v>
       </c>
-      <c r="G17" s="23" t="n">
+      <c r="G18" s="8" t="n">
         <v>63205</v>
       </c>
-      <c r="H17" s="23" t="n">
+      <c r="H18" s="8" t="n">
         <v>5341</v>
       </c>
-      <c r="I17" s="23" t="n">
+      <c r="I18" s="8" t="n">
         <v>5796</v>
       </c>
-      <c r="J17" s="23" t="n">
+      <c r="J18" s="8" t="n">
         <v>4234</v>
       </c>
-      <c r="K17" s="23" t="n">
+      <c r="K18" s="8" t="n">
         <v>3979</v>
       </c>
-      <c r="L17" s="24" t="n">
+      <c r="L18" s="23" t="n">
         <v>132538</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>14 Sep</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C19" s="13" t="n">
         <v>22478</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D19" s="13" t="n">
         <v>11127</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E19" s="13" t="n">
         <v>9908</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F19" s="13" t="n">
         <v>15200</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G19" s="13" t="n">
         <v>52561</v>
       </c>
-      <c r="H18" s="11" t="n">
+      <c r="H19" s="13" t="n">
         <v>6207</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I19" s="13" t="n">
         <v>8534</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J19" s="13" t="n">
         <v>3967</v>
       </c>
-      <c r="K18" s="11" t="n">
+      <c r="K19" s="13" t="n">
         <v>4530</v>
       </c>
-      <c r="L18" s="13" t="n">
+      <c r="L19" s="23" t="n">
         <v>134512</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>15 Sep</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C20" s="8" t="n">
         <v>22334</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D20" s="8" t="n">
         <v>14883</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E20" s="8" t="n">
         <v>6999</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F20" s="8" t="n">
         <v>11296</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G20" s="8" t="n">
         <v>64421</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H20" s="8" t="n">
         <v>3696</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I20" s="8" t="n">
         <v>9485</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J20" s="8" t="n">
         <v>5068</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="K20" s="8" t="n">
         <v>5380</v>
       </c>
-      <c r="L19" s="8" t="n">
+      <c r="L20" s="23" t="n">
         <v>143562</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>16 Sep</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C21" s="13" t="n">
         <v>26929</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D21" s="13" t="n">
         <v>11544</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E21" s="13" t="n">
         <v>8847</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F21" s="13" t="n">
         <v>11416</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G21" s="13" t="n">
         <v>67288</v>
       </c>
-      <c r="H20" s="11" t="n">
+      <c r="H21" s="13" t="n">
         <v>6230</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I21" s="13" t="n">
         <v>7086</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J21" s="13" t="n">
         <v>5494</v>
       </c>
-      <c r="K20" s="11" t="n">
+      <c r="K21" s="13" t="n">
         <v>6694</v>
       </c>
-      <c r="L20" s="13" t="n">
+      <c r="L21" s="23" t="n">
         <v>151528</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>17 Sep</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C22" s="8" t="n">
         <v>29291</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D22" s="8" t="n">
         <v>19082</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E22" s="8" t="n">
         <v>8520</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F22" s="8" t="n">
         <v>15363</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G22" s="8" t="n">
         <v>81775</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H22" s="8" t="n">
         <v>5770</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I22" s="8" t="n">
         <v>7254</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J22" s="8" t="n">
         <v>8613</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K22" s="8" t="n">
         <v>6115</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L22" s="23" t="n">
         <v>181783</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>18 Sep</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C23" s="13" t="n">
         <v>21968</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D23" s="13" t="n">
         <v>9989</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E23" s="13" t="n">
         <v>10581</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F23" s="13" t="n">
         <v>14531</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G23" s="13" t="n">
         <v>62568</v>
       </c>
-      <c r="H22" s="11" t="n">
+      <c r="H23" s="13" t="n">
         <v>4491</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I23" s="13" t="n">
         <v>7862</v>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J23" s="13" t="n">
         <v>2376</v>
       </c>
-      <c r="K22" s="11" t="n">
+      <c r="K23" s="13" t="n">
         <v>5499</v>
       </c>
-      <c r="L22" s="13" t="n">
+      <c r="L23" s="23" t="n">
         <v>139865</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>19 Sep</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C24" s="8" t="n">
         <v>22631</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D24" s="8" t="n">
         <v>7487</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E24" s="8" t="n">
         <v>8625</v>
       </c>
-      <c r="F23" s="23" t="n">
+      <c r="F24" s="8" t="n">
         <v>8898</v>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="G24" s="8" t="n">
         <v>52473</v>
       </c>
-      <c r="H23" s="23" t="n">
+      <c r="H24" s="8" t="n">
         <v>3178</v>
       </c>
-      <c r="I23" s="23" t="n">
+      <c r="I24" s="8" t="n">
         <v>5710</v>
       </c>
-      <c r="J23" s="23" t="n">
+      <c r="J24" s="8" t="n">
         <v>3257</v>
       </c>
-      <c r="K23" s="23" t="n">
+      <c r="K24" s="8" t="n">
         <v>3054</v>
       </c>
-      <c r="L23" s="24" t="n">
+      <c r="L24" s="23" t="n">
         <v>115313</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>20 Sep</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C25" s="13" t="n">
         <v>22946</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D25" s="13" t="n">
         <v>16001</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E25" s="13" t="n">
         <v>7850</v>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F25" s="13" t="n">
         <v>15725</v>
       </c>
-      <c r="G24" s="23" t="n">
+      <c r="G25" s="13" t="n">
         <v>73061</v>
       </c>
-      <c r="H24" s="23" t="n">
+      <c r="H25" s="13" t="n">
         <v>4001</v>
       </c>
-      <c r="I24" s="23" t="n">
+      <c r="I25" s="13" t="n">
         <v>4459</v>
       </c>
-      <c r="J24" s="23" t="n">
+      <c r="J25" s="13" t="n">
         <v>2951</v>
       </c>
-      <c r="K24" s="23" t="n">
+      <c r="K25" s="13" t="n">
         <v>6278</v>
       </c>
-      <c r="L24" s="24" t="n">
+      <c r="L25" s="23" t="n">
         <v>153272</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>21 Sep</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C26" s="8" t="n">
         <v>24811</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D26" s="8" t="n">
         <v>12789</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E26" s="8" t="n">
         <v>7877</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F26" s="8" t="n">
         <v>16910</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G26" s="8" t="n">
         <v>76815</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H26" s="8" t="n">
         <v>4592</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I26" s="8" t="n">
         <v>5755</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J26" s="8" t="n">
         <v>2483</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="K26" s="8" t="n">
         <v>5159</v>
       </c>
-      <c r="L25" s="8" t="n">
+      <c r="L26" s="23" t="n">
         <v>157191</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>22 Sep</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C27" s="13" t="n">
         <v>25978</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D27" s="13" t="n">
         <v>11048</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E27" s="13" t="n">
         <v>13107</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F27" s="13" t="n">
         <v>11848</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G27" s="13" t="n">
         <v>81833</v>
       </c>
-      <c r="H26" s="11" t="n">
+      <c r="H27" s="13" t="n">
         <v>6303</v>
       </c>
-      <c r="I26" s="11" t="n">
+      <c r="I27" s="13" t="n">
         <v>7663</v>
       </c>
-      <c r="J26" s="11" t="n">
+      <c r="J27" s="13" t="n">
         <v>4226</v>
       </c>
-      <c r="K26" s="11" t="n">
+      <c r="K27" s="13" t="n">
         <v>6830</v>
       </c>
-      <c r="L26" s="13" t="n">
+      <c r="L27" s="23" t="n">
         <v>168836</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>23 Sep</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C28" s="8" t="n">
         <v>24138</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D28" s="8" t="n">
         <v>13280</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E28" s="8" t="n">
         <v>11400</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F28" s="8" t="n">
         <v>12644</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G28" s="8" t="n">
         <v>74228</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H28" s="8" t="n">
         <v>8750</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I28" s="8" t="n">
         <v>8285</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J28" s="8" t="n">
         <v>6556</v>
       </c>
-      <c r="K27" s="6" t="n">
+      <c r="K28" s="8" t="n">
         <v>5496</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L28" s="23" t="n">
         <v>164777</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>24 Sep</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C29" s="13" t="n">
         <v>23356</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D29" s="13" t="n">
         <v>11615</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E29" s="13" t="n">
         <v>8637</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F29" s="13" t="n">
         <v>12351</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G29" s="13" t="n">
         <v>66113</v>
       </c>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="11" t="n">
+      <c r="H29" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="n">
         <v>5940</v>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="J29" s="13" t="n">
         <v>7387</v>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="K29" s="13" t="n">
         <v>5010</v>
       </c>
-      <c r="L28" s="13" t="n">
+      <c r="L29" s="23" t="n">
         <v>140409</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>25 Sep</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C30" s="8" t="n">
         <v>25322</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D30" s="8" t="n">
         <v>12322</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E30" s="8" t="n">
         <v>9430</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F30" s="8" t="n">
         <v>13256</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G30" s="8" t="n">
         <v>82534</v>
       </c>
-      <c r="H29" s="26" t="n"/>
-      <c r="I29" s="6" t="n">
+      <c r="H30" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="n">
         <v>5001</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J30" s="8" t="n">
         <v>10087</v>
       </c>
-      <c r="K29" s="6" t="n">
+      <c r="K30" s="8" t="n">
         <v>4250</v>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="L30" s="23" t="n">
         <v>162202</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>26 Sep</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C31" s="13" t="n">
         <v>21963</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D31" s="13" t="n">
         <v>9896</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E31" s="13" t="n">
         <v>1563</v>
       </c>
-      <c r="F30" s="23" t="n">
+      <c r="F31" s="13" t="n">
         <v>2251</v>
       </c>
-      <c r="G30" s="23" t="n">
+      <c r="G31" s="13" t="n">
         <v>55960</v>
       </c>
-      <c r="H30" s="27" t="n"/>
-      <c r="I30" s="23" t="n">
+      <c r="H31" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="n">
         <v>689</v>
       </c>
-      <c r="J30" s="23" t="n">
+      <c r="J31" s="13" t="n">
         <v>1661</v>
       </c>
-      <c r="K30" s="23" t="n">
+      <c r="K31" s="13" t="n">
         <v>1969</v>
       </c>
-      <c r="L30" s="24" t="n">
+      <c r="L31" s="23" t="n">
         <v>95952</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>27 Sep</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C32" s="8" t="n">
         <v>23968</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D32" s="8" t="n">
         <v>11998</v>
       </c>
-      <c r="E31" s="23" t="n">
+      <c r="E32" s="8" t="n">
         <v>9483</v>
       </c>
-      <c r="F31" s="23" t="n">
+      <c r="F32" s="8" t="n">
         <v>10834</v>
       </c>
-      <c r="G31" s="23" t="n">
+      <c r="G32" s="8" t="n">
         <v>70457</v>
       </c>
-      <c r="H31" s="27" t="n"/>
-      <c r="I31" s="23" t="n">
+      <c r="H32" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="n">
         <v>4088</v>
       </c>
-      <c r="J31" s="23" t="n">
+      <c r="J32" s="8" t="n">
         <v>12805</v>
       </c>
-      <c r="K31" s="23" t="n">
+      <c r="K32" s="8" t="n">
         <v>4183</v>
       </c>
-      <c r="L31" s="24" t="n">
+      <c r="L32" s="23" t="n">
         <v>147816</v>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B32" s="28" t="inlineStr"/>
-      <c r="C32" s="29" t="n">
+      <c r="B33" s="30" t="inlineStr"/>
+      <c r="C33" s="31" t="n">
         <v>600608</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D33" s="31" t="n">
         <v>360844</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E33" s="31" t="n">
         <v>254054</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F33" s="31" t="n">
         <v>362373</v>
       </c>
-      <c r="G32" s="29" t="n">
+      <c r="G33" s="31" t="n">
         <v>1525912</v>
       </c>
-      <c r="H32" s="29" t="n">
+      <c r="H33" s="31" t="n">
         <v>150916</v>
       </c>
-      <c r="I32" s="29" t="n">
+      <c r="I33" s="31" t="n">
         <v>211006</v>
       </c>
-      <c r="J32" s="29" t="n">
+      <c r="J33" s="31" t="n">
         <v>81165</v>
       </c>
-      <c r="K32" s="29" t="n">
+      <c r="K33" s="31" t="n">
         <v>150988</v>
       </c>
-      <c r="L32" s="30" t="n">
+      <c r="L33" s="32" t="n">
         <v>3697866</v>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="31" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t>SHARE %</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="32" t="n">
+      <c r="B34" s="34" t="inlineStr"/>
+      <c r="C34" s="36" t="n">
         <v>0.1624201634131686</v>
       </c>
-      <c r="D33" s="32" t="n">
+      <c r="D34" s="36" t="n">
         <v>0.09758168630231598</v>
       </c>
-      <c r="E33" s="32" t="n">
+      <c r="E34" s="36" t="n">
         <v>0.06870286808662077</v>
       </c>
-      <c r="F33" s="32" t="n">
+      <c r="F34" s="36" t="n">
         <v>0.09799516802393597</v>
       </c>
-      <c r="G33" s="32" t="n">
+      <c r="G34" s="35" t="n">
         <v>0.4126466453895301</v>
       </c>
-      <c r="H33" s="32" t="n">
+      <c r="H34" s="36" t="n">
         <v>0.04081164650098192</v>
       </c>
-      <c r="I33" s="32" t="n">
+      <c r="I34" s="36" t="n">
         <v>0.05706155928851938</v>
       </c>
-      <c r="J33" s="32" t="n">
+      <c r="J34" s="36" t="n">
         <v>0.02194914580463435</v>
       </c>
-      <c r="K33" s="32" t="n">
+      <c r="K34" s="36" t="n">
         <v>0.040831117190293</v>
       </c>
-      <c r="L33" s="33" t="n">
+      <c r="L34" s="37" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="34" t="inlineStr">
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="38" t="inlineStr">
         <is>
           <t>ZONE SUMMARY  —  September 2026</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+    <row r="37" ht="3" customHeight="1">
+      <c r="A37" s="3" t="n"/>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="39" t="inlineStr">
         <is>
           <t>Zone Grand Total</t>
         </is>
       </c>
-      <c r="B36" s="36" t="inlineStr">
-        <is>
-          <t>₹3,697,866</t>
-        </is>
-      </c>
-      <c r="C36" s="37" t="n"/>
-      <c r="D36" s="37" t="n"/>
-      <c r="E36" s="37" t="n"/>
-      <c r="F36" s="37" t="n"/>
-      <c r="G36" s="37" t="n"/>
-      <c r="H36" s="37" t="n"/>
-      <c r="I36" s="37" t="n"/>
-      <c r="J36" s="37" t="n"/>
-      <c r="K36" s="37" t="n"/>
-      <c r="L36" s="37" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
+        <is>
+          <t>₹36,97,866</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="n"/>
+      <c r="D38" s="41" t="n"/>
+      <c r="E38" s="41" t="n"/>
+      <c r="F38" s="41" t="n"/>
+      <c r="G38" s="41" t="n"/>
+      <c r="H38" s="41" t="n"/>
+      <c r="I38" s="41" t="n"/>
+      <c r="J38" s="41" t="n"/>
+      <c r="K38" s="41" t="n"/>
+      <c r="L38" s="41" t="n"/>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="A39" s="39" t="inlineStr">
         <is>
           <t>Operating Days</t>
         </is>
       </c>
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B39" s="42" t="inlineStr">
         <is>
           <t>27 days</t>
         </is>
       </c>
-      <c r="C37" s="37" t="n"/>
-      <c r="D37" s="37" t="n"/>
-      <c r="E37" s="37" t="n"/>
-      <c r="F37" s="37" t="n"/>
-      <c r="G37" s="37" t="n"/>
-      <c r="H37" s="37" t="n"/>
-      <c r="I37" s="37" t="n"/>
-      <c r="J37" s="37" t="n"/>
-      <c r="K37" s="37" t="n"/>
-      <c r="L37" s="37" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="41" t="n"/>
+      <c r="E39" s="41" t="n"/>
+      <c r="F39" s="41" t="n"/>
+      <c r="G39" s="41" t="n"/>
+      <c r="H39" s="41" t="n"/>
+      <c r="I39" s="41" t="n"/>
+      <c r="J39" s="41" t="n"/>
+      <c r="K39" s="41" t="n"/>
+      <c r="L39" s="41" t="n"/>
+    </row>
+    <row r="40" ht="21" customHeight="1">
+      <c r="A40" s="39" t="inlineStr">
         <is>
           <t>Average Daily Sales</t>
         </is>
       </c>
-      <c r="B38" s="36" t="inlineStr">
-        <is>
-          <t>₹136,958</t>
-        </is>
-      </c>
-      <c r="C38" s="37" t="n"/>
-      <c r="D38" s="37" t="n"/>
-      <c r="E38" s="37" t="n"/>
-      <c r="F38" s="37" t="n"/>
-      <c r="G38" s="37" t="n"/>
-      <c r="H38" s="37" t="n"/>
-      <c r="I38" s="37" t="n"/>
-      <c r="J38" s="37" t="n"/>
-      <c r="K38" s="37" t="n"/>
-      <c r="L38" s="37" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="B40" s="42" t="inlineStr">
+        <is>
+          <t>₹1,36,958</t>
+        </is>
+      </c>
+      <c r="C40" s="41" t="n"/>
+      <c r="D40" s="41" t="n"/>
+      <c r="E40" s="41" t="n"/>
+      <c r="F40" s="41" t="n"/>
+      <c r="G40" s="41" t="n"/>
+      <c r="H40" s="41" t="n"/>
+      <c r="I40" s="41" t="n"/>
+      <c r="J40" s="41" t="n"/>
+      <c r="K40" s="41" t="n"/>
+      <c r="L40" s="41" t="n"/>
+    </row>
+    <row r="41" ht="21" customHeight="1">
+      <c r="A41" s="39" t="inlineStr">
         <is>
           <t>Best Sales Day</t>
         </is>
       </c>
-      <c r="B39" s="36" t="inlineStr">
-        <is>
-          <t>17 Sep (Thursday) — ₹181,783</t>
-        </is>
-      </c>
-      <c r="C39" s="37" t="n"/>
-      <c r="D39" s="37" t="n"/>
-      <c r="E39" s="37" t="n"/>
-      <c r="F39" s="37" t="n"/>
-      <c r="G39" s="37" t="n"/>
-      <c r="H39" s="37" t="n"/>
-      <c r="I39" s="37" t="n"/>
-      <c r="J39" s="37" t="n"/>
-      <c r="K39" s="37" t="n"/>
-      <c r="L39" s="37" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="B41" s="42" t="inlineStr">
+        <is>
+          <t>17 Sep (Thursday)  •  ₹1,81,783</t>
+        </is>
+      </c>
+      <c r="C41" s="41" t="n"/>
+      <c r="D41" s="41" t="n"/>
+      <c r="E41" s="41" t="n"/>
+      <c r="F41" s="41" t="n"/>
+      <c r="G41" s="41" t="n"/>
+      <c r="H41" s="41" t="n"/>
+      <c r="I41" s="41" t="n"/>
+      <c r="J41" s="41" t="n"/>
+      <c r="K41" s="41" t="n"/>
+      <c r="L41" s="41" t="n"/>
+    </row>
+    <row r="42" ht="21" customHeight="1">
+      <c r="A42" s="39" t="inlineStr">
         <is>
           <t>Top Brand</t>
         </is>
       </c>
-      <c r="B40" s="36" t="inlineStr">
-        <is>
-          <t>B2B — ₹1,525,912 (41.3%)</t>
-        </is>
-      </c>
-      <c r="C40" s="37" t="n"/>
-      <c r="D40" s="37" t="n"/>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="37" t="n"/>
-      <c r="G40" s="37" t="n"/>
-      <c r="H40" s="37" t="n"/>
-      <c r="I40" s="37" t="n"/>
-      <c r="J40" s="37" t="n"/>
-      <c r="K40" s="37" t="n"/>
-      <c r="L40" s="37" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="35" t="inlineStr">
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>B2B  •  ₹15,25,912  (41.3%)</t>
+        </is>
+      </c>
+      <c r="C42" s="41" t="n"/>
+      <c r="D42" s="41" t="n"/>
+      <c r="E42" s="41" t="n"/>
+      <c r="F42" s="41" t="n"/>
+      <c r="G42" s="41" t="n"/>
+      <c r="H42" s="41" t="n"/>
+      <c r="I42" s="41" t="n"/>
+      <c r="J42" s="41" t="n"/>
+      <c r="K42" s="41" t="n"/>
+      <c r="L42" s="41" t="n"/>
+    </row>
+    <row r="43" ht="21" customHeight="1">
+      <c r="A43" s="39" t="inlineStr">
         <is>
           <t>Active Brands</t>
         </is>
       </c>
-      <c r="B41" s="36" t="inlineStr">
+      <c r="B43" s="42" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C41" s="37" t="n"/>
-      <c r="D41" s="37" t="n"/>
-      <c r="E41" s="37" t="n"/>
-      <c r="F41" s="37" t="n"/>
-      <c r="G41" s="37" t="n"/>
-      <c r="H41" s="37" t="n"/>
-      <c r="I41" s="37" t="n"/>
-      <c r="J41" s="37" t="n"/>
-      <c r="K41" s="37" t="n"/>
-      <c r="L41" s="37" t="n"/>
+      <c r="C43" s="41" t="n"/>
+      <c r="D43" s="41" t="n"/>
+      <c r="E43" s="41" t="n"/>
+      <c r="F43" s="41" t="n"/>
+      <c r="G43" s="41" t="n"/>
+      <c r="H43" s="41" t="n"/>
+      <c r="I43" s="41" t="n"/>
+      <c r="J43" s="41" t="n"/>
+      <c r="K43" s="41" t="n"/>
+      <c r="L43" s="41" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>Weekends shown in red • – denotes no recorded sale • all totals recomputed from daily brand-wise figures</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="12">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="B41:L41"/>
+    <mergeCell ref="B43:L43"/>
     <mergeCell ref="B38:L38"/>
     <mergeCell ref="B39:L39"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B37:L37"/>
-    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="A3:L3"/>
     <mergeCell ref="B40:L40"/>
-    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="B41:L41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SEPTEMBER 2026 - ZONE SALES REPORT.xlsx
+++ b/SEPTEMBER 2026 - ZONE SALES REPORT.xlsx
@@ -50,24 +50,24 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="00141414"/>
+      <color rgb="002F3E45"/>
       <sz val="10.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="005A5A5A"/>
+      <color rgb="005C6B72"/>
       <sz val="10.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00141414"/>
+      <color rgb="002F3E45"/>
       <sz val="10.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00D02128"/>
+      <color rgb="004F7D6E"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -95,29 +95,29 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="005A5A5A"/>
+      <color rgb="005C6B72"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="00141414"/>
+      <color rgb="002F3E45"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00D02128"/>
+      <color rgb="004F7D6E"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="005A5A5A"/>
+      <color rgb="005C6B72"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00141414"/>
+      <color rgb="002F3E45"/>
       <sz val="10"/>
     </font>
     <font>
@@ -129,31 +129,31 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="005A5A5A"/>
+      <color rgb="005C6B72"/>
       <sz val="10.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00D02128"/>
+      <color rgb="004F7D6E"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <i val="1"/>
-      <color rgb="008A8A8A"/>
+      <color rgb="008B969D"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00141414"/>
+      <color rgb="002F3E45"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00D02128"/>
+      <color rgb="004F7D6E"/>
       <sz val="11"/>
     </font>
     <font>
@@ -165,7 +165,7 @@
     <font>
       <name val="Segoe UI"/>
       <i val="1"/>
-      <color rgb="008A8A8A"/>
+      <color rgb="008B969D"/>
       <sz val="9.5"/>
     </font>
   </fonts>
@@ -178,17 +178,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000A0A0A"/>
+        <fgColor rgb="0034515B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D02128"/>
+        <fgColor rgb="004F7D6E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A1A1A"/>
+        <fgColor rgb="004A6D76"/>
       </patternFill>
     </fill>
     <fill>
@@ -198,12 +198,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F4F4"/>
+        <fgColor rgb="00EDF2EF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAFAFA"/>
+        <fgColor rgb="00F7F5F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -217,16 +217,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E6E6E6"/>
+        <color rgb="00E7E2D9"/>
       </left>
       <right style="thin">
-        <color rgb="00E6E6E6"/>
+        <color rgb="00E7E2D9"/>
       </right>
       <top style="thin">
-        <color rgb="00E6E6E6"/>
+        <color rgb="00E7E2D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E6E6E6"/>
+        <color rgb="00E7E2D9"/>
       </bottom>
     </border>
   </borders>
@@ -743,7 +743,7 @@
             <rPr>
               <rFont val="Segoe UI"/>
               <b val="1"/>
-              <color rgb="FFEF4444"/>
+              <color rgb="FF9BC3B6"/>
               <sz val="22"/>
             </rPr>
             <t>S</t>
@@ -938,7 +938,7 @@
             <rPr>
               <rFont val="Segoe UI"/>
               <b val="1"/>
-              <color rgb="FFEF4444"/>
+              <color rgb="FF9BC3B6"/>
               <sz val="22"/>
             </rPr>
             <t>A</t>
@@ -2033,7 +2033,7 @@
             <rPr>
               <rFont val="Segoe UI"/>
               <b val="1"/>
-              <color rgb="FFEF4444"/>
+              <color rgb="FF9BC3B6"/>
               <sz val="22"/>
             </rPr>
             <t>C</t>
@@ -3151,7 +3151,7 @@
             <rPr>
               <rFont val="Segoe UI"/>
               <b val="1"/>
-              <color rgb="FFEF4444"/>
+              <color rgb="FF9BC3B6"/>
               <sz val="22"/>
             </rPr>
             <t>B</t>
